--- a/output/roomself_excel/1230.xlsx
+++ b/output/roomself_excel/1230.xlsx
@@ -479,7 +479,7 @@
         <v>910</v>
       </c>
       <c r="F2" t="n">
-        <v>910</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>2804</v>
       </c>
       <c r="E3" t="n">
-        <v>910</v>
+        <v>400</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2684</v>
       </c>
       <c r="E5" t="n">
-        <v>910</v>
+        <v>476</v>
       </c>
       <c r="F5" t="n">
         <v>180</v>

--- a/output/roomself_excel/1230.xlsx
+++ b/output/roomself_excel/1230.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>4552</v>
       </c>
-      <c r="E2" t="n">
-        <v>910</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>433</v>
+        <v>1313</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>391</v>
+      </c>
+      <c r="J2" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>2804</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>400</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>19</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>301</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>2796</v>
       </c>
-      <c r="E4" t="n">
-        <v>193</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2684</v>
       </c>
-      <c r="E5" t="n">
-        <v>476</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>446</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>160</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>1272</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +661,26 @@
       <c r="D7" t="n">
         <v>2508</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>234</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>393</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>20</v>
       </c>
     </row>
